--- a/scripts/fixtures/recebimentos-exemplo-baixa.xlsx
+++ b/scripts/fixtures/recebimentos-exemplo-baixa.xlsx
@@ -863,13 +863,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DFC8F281-5893-4802-B075-160EBB91035C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3F51F24-116C-4AFF-8F83-B73AE5BB373F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0271910-A1AA-4E53-B29E-A5EFF0351BF4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D28E9E8-0760-44F5-8D1F-677C940DD9A6}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5364396A-C179-4798-AB10-171C8F488944}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59CF13BC-96EF-46D6-B982-A0CD67FE4D2D}"/>
 </file>